--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128153567</v>
+        <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>92632</v>
+        <v>98385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627872</v>
+        <v>627854</v>
       </c>
       <c r="R5" t="n">
-        <v>6921162</v>
+        <v>6921168</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1088,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128152186</v>
+        <v>128207235</v>
       </c>
       <c r="B6" t="n">
         <v>98468</v>
@@ -1158,24 +1158,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627876</v>
+        <v>627847</v>
       </c>
       <c r="R6" t="n">
-        <v>6921128</v>
+        <v>6921143</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,22 +1195,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,54 +1237,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128152043</v>
+        <v>128153567</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627863</v>
+        <v>627872</v>
       </c>
       <c r="R7" t="n">
-        <v>6921121</v>
+        <v>6921162</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1320,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128152434</v>
+        <v>128152186</v>
       </c>
       <c r="B8" t="n">
         <v>98468</v>
@@ -1387,12 +1374,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1401,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627885</v>
+        <v>627876</v>
       </c>
       <c r="R8" t="n">
-        <v>6921119</v>
+        <v>6921128</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1436,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,6 +1452,238 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128152043</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627863</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6921121</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128152434</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627885</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6921119</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,45 +1237,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128153567</v>
+        <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>92632</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627872</v>
+        <v>627876</v>
       </c>
       <c r="R7" t="n">
-        <v>6921162</v>
+        <v>6921128</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1307,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128152186</v>
+        <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1378,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1383,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627876</v>
+        <v>627863</v>
       </c>
       <c r="R8" t="n">
-        <v>6921128</v>
+        <v>6921121</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1418,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128152043</v>
+        <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,7 +1494,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1499,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627863</v>
+        <v>627885</v>
       </c>
       <c r="R9" t="n">
-        <v>6921121</v>
+        <v>6921119</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1534,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,122 +1577,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>128152434</v>
-      </c>
-      <c r="B10" t="n">
-        <v>98468</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>627885</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6921119</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Alnö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Anna Nordbäck</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Anna Nordbäck</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151889</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128152110</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128151927</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128152186</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128152043</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128152434</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128207183</v>
       </c>
       <c r="B5" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128207235</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36001-2025 artfynd.xlsx
+++ b/artfynd/A 36001-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128151889</v>
+        <v>97660075</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+          <t>Hovbergsstugan, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627811</v>
+        <v>627760</v>
       </c>
       <c r="R2" t="n">
-        <v>6921099</v>
+        <v>6921142</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,69 +777,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Henrik Westberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Henrik Westberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128152110</v>
+        <v>128207183</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627855</v>
+        <v>627854</v>
       </c>
       <c r="R3" t="n">
-        <v>6921118</v>
+        <v>6921168</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,32 +896,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128151927</v>
+        <v>128151444</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627833</v>
+        <v>627776</v>
       </c>
       <c r="R4" t="n">
-        <v>6921105</v>
+        <v>6921086</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,48 +1012,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128207183</v>
+        <v>128151406</v>
       </c>
       <c r="B5" t="n">
-        <v>98536</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627854</v>
+        <v>627765</v>
       </c>
       <c r="R5" t="n">
-        <v>6921168</v>
+        <v>6921084</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128207235</v>
+        <v>128151669</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,20 +1156,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627847</v>
+        <v>627790</v>
       </c>
       <c r="R6" t="n">
-        <v>6921143</v>
+        <v>6921086</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,22 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128152186</v>
+        <v>128151775</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1274,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1276,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627876</v>
+        <v>627810</v>
       </c>
       <c r="R7" t="n">
-        <v>6921128</v>
+        <v>6921092</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1311,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128152043</v>
+        <v>128151889</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,7 +1390,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1392,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627863</v>
+        <v>627811</v>
       </c>
       <c r="R8" t="n">
-        <v>6921121</v>
+        <v>6921099</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1427,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128152434</v>
+        <v>128151927</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627885</v>
+        <v>627833</v>
       </c>
       <c r="R9" t="n">
-        <v>6921119</v>
+        <v>6921105</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1543,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,6 +1589,1455 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128152043</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627863</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6921121</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128152110</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627855</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6921118</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128152186</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>627876</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6921128</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128152434</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627885</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6921119</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128153708</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627835</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6921202</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128153743</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627828</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6921202</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128154029</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>627880</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6921206</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128206962</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hovberget, Hovberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>627813</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6921192</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128206989</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hovberget, Hovberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>627833</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6921208</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128207235</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>627847</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6921143</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128207452</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hovberget, Hovberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>627835</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6921206</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128207514</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hovberget, Hovberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>627815</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6921202</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128207698</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>627892</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6921199</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
